--- a/SauceDemo_Test_Execution_Sheet.xlsx
+++ b/SauceDemo_Test_Execution_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Pc\Desktop\SauceDemo_QA_Project\02_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8528763-9161-4AB6-A005-7A4973C70638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E2B4AD-9540-4627-8E79-D86CE5F11801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{465A810A-70C6-446D-8C82-D33575437629}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="119">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -465,6 +465,18 @@
       </rPr>
       <t>secret_sauce</t>
     </r>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -679,7 +691,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
@@ -691,6 +703,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -727,6 +740,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1052,583 +1072,638 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA4342E-E0E0-4312-B9F5-F7E10AD8C19C}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="30.33203125" customWidth="1"/>
-    <col min="7" max="7" width="37.21875" customWidth="1"/>
-    <col min="8" max="8" width="36.109375" customWidth="1"/>
-    <col min="9" max="9" width="39" customWidth="1"/>
-    <col min="10" max="10" width="36.77734375" customWidth="1"/>
+    <col min="2" max="3" width="31.44140625" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.44140625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="37.21875" customWidth="1"/>
+    <col min="9" max="9" width="36.109375" customWidth="1"/>
+    <col min="10" max="10" width="39" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="7"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="24"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="5">
         <v>46273</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="24"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="5">
         <v>46273</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" s="21" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="C8" s="25"/>
+    </row>
+    <row r="11" spans="1:12" s="22" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="E11" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="H11" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="J11" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="K11" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="L11" s="21"/>
+    </row>
+    <row r="12" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:11" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" spans="1:12" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="I14" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:12" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="I15" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" ht="84" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:12" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="I16" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="1:10" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="I17" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="F18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I18" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="I21" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="J21" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="I22" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="1:10" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="1:11" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="G23" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="I23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="J23" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" spans="1:10" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="1:11" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="F24" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="G24" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="I24" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" spans="1:10" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C27" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="G27" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="I27" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="J27" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" spans="1:10" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" spans="1:11" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C28" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="F28" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J28" s="9"/>
-    </row>
-    <row r="29" spans="1:10" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" spans="1:11" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="G29" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="I29" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="J29" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J29" s="9"/>
-    </row>
-    <row r="30" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="F30" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="G30" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="H30" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="I30" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="J30" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="K30" s="11" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:J26"/>
-    <mergeCell ref="A12:J13"/>
-    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A25:K26"/>
+    <mergeCell ref="A12:K13"/>
+    <mergeCell ref="A19:K20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
